--- a/tables_and_figures/table3_jaccard_pairs.xlsx
+++ b/tables_and_figures/table3_jaccard_pairs.xlsx
@@ -419,32 +419,32 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>SAQLI</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>OSAPOSI</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>QSQ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MOSAS</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>PRAQ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>SAQLI</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>QSQ</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>OSAPOSI</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>STAMP</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>MOSAS</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -456,57 +456,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PRAQ</t>
+          <t>SAQLI</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4230769230769231</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.6296296296296297</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.3571428571428572</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SAQLI</t>
+          <t>OSAPOSI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5</v>
       </c>
       <c r="H4" t="n">
         <v>0.2692307692307692</v>
@@ -540,85 +540,85 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OSAPOSI</t>
+          <t>MOSAS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="H5" t="n">
-        <v>0.35</v>
+        <v>0.2352941176470588</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STAMP</t>
+          <t>PRAQ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2962962962962963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MOSAS</t>
+          <t>STAMP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -628,22 +628,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.35</v>
       </c>
       <c r="D8" t="n">
         <v>0.2692307692307692</v>
       </c>
       <c r="E8" t="n">
-        <v>0.35</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="F8" t="n">
+        <v>0.2962962962962963</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.1666666666666667</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.2352941176470588</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
